--- a/data/relay_table.xlsx
+++ b/data/relay_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tongzhao/Documents/Claude_Code/中转站对比小网页/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F852F12F-4EF8-CA43-8127-94A66BA84209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880BD81D-240C-E24C-984E-C6CE38219979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="relay_table" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
   <si>
     <t>中转站名称</t>
   </si>
@@ -77,110 +77,124 @@
     <t>每天都在用</t>
   </si>
   <si>
+    <t>富可敌国</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>共充值10元</t>
+  </si>
+  <si>
+    <t>[Tiger（虎）](https://tiger.bookapi.cc/ref/C5E3)</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>共充值50元</t>
+  </si>
+  <si>
+    <t>[RightCode](https://www.right.codes/register?aff=7845fdb4)</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>小股东套餐使用中，共充值13元</t>
+  </si>
+  <si>
+    <t>主站可签到，令有[公益站](https://free.duckcoding.com/register?aff=ZRcQ)，kiro反代</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>[NekoCode](https://nekocode.ai?aff=TRPTNGM8)</t>
+  </si>
+  <si>
+    <t>订阅制&lt;br /&gt;本统计按Pro套餐计算（299¥/月，可使用600$）</t>
+  </si>
+  <si>
+    <t>[HorseCoding（马）](https://www.horsecoding.cc)</t>
+  </si>
+  <si>
+    <t>他家有cc分组和claude-offical分组，我这里是按照cc分组来统计的</t>
+  </si>
+  <si>
+    <t>最低充值30</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>9.9刀按量、另有订阅&lt;br /&gt;根据[官方说法](https://linux.do/t/topic/1510513/8?u=tongzhao)订阅 0.75 CNY/USD，按量 1.5 CNY/USD &lt;br /&gt;春节期间倍率为0.7，本统计按日常价格计算。&lt;br /&gt;有日限/周限</t>
+  </si>
+  <si>
+    <t>购买19.9套餐</t>
+  </si>
+  <si>
+    <t>[FoxCode(狐狸)](https://foxcode.rjj.cc/auth/register?aff=6W5J31UI)</t>
+  </si>
+  <si>
+    <t>linkflow</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>需私聊上车，[站内地址](https://linux.do/t/topic/1092606)</t>
+  </si>
+  <si>
+    <t>汇率 &lt;br /&gt; 1$=?¥</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最低消费（充值）&lt;br /&gt;（单位：¥）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~~刚开业，优惠价为0.7RMB1刀~~优惠结束，现汇率改为1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~~最低充值50~~最低充值100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~~官渠暂时不可用~~ &lt;br /&gt;官渠恢复，倍率调整至7.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[PackyCode（老农）](https://www.packyapi.com/register?aff=grZq)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Cubence(鹅)](https://cubence.com/signup?code=SCTG7GCQ)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[YesCode](https://co.yes.vg/register?ref=TongZhao)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>[iKun（鸡）](https://api.ikuncode.cc/register?aff=1izN)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[DuckCoding（鸭）](https://duckcoding.com/register?aff=pQIu)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[MonkingAI(猴)](https://www.monking.ai/register?aff=1kvd)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>富可敌国</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>共充值10元</t>
-  </si>
-  <si>
-    <t>[Tiger（虎）](https://tiger.bookapi.cc/ref/C5E3)</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>0.7</t>
-  </si>
-  <si>
-    <t>共充值50元</t>
-  </si>
-  <si>
-    <t>[RightCode](https://www.right.codes/register?aff=7845fdb4)</t>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>小股东套餐使用中，共充值13元</t>
-  </si>
-  <si>
-    <t>[DuckCoding（鸭）](https://duckcoding.com/register?aff=pQIu)</t>
-  </si>
-  <si>
-    <t>主站可签到，令有[公益站](https://free.duckcoding.com/register?aff=ZRcQ)，kiro反代</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>[NekoCode](https://nekocode.ai?aff=TRPTNGM8)</t>
-  </si>
-  <si>
-    <t>订阅制&lt;br /&gt;本统计按Pro套餐计算（299¥/月，可使用600$）</t>
-  </si>
-  <si>
-    <t>[HorseCoding（马）](https://www.horsecoding.cc)</t>
-  </si>
-  <si>
-    <t>[PackyCode（老农）](https://www.packyapi.com/register?aff=grZq)</t>
-  </si>
-  <si>
-    <t>他家有cc分组和claude-offical分组，我这里是按照cc分组来统计的</t>
-  </si>
-  <si>
-    <t>[Cubence(鹅)](https://cubence.com/signup?code=SCTG7GCQ)</t>
-  </si>
-  <si>
-    <t>最低充值30</t>
-  </si>
-  <si>
-    <t>[YesCode](https://co.yes.vg/register?ref=TongZhao)</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>9.9刀按量、另有订阅&lt;br /&gt;根据[官方说法](https://linux.do/t/topic/1510513/8?u=tongzhao)订阅 0.75 CNY/USD，按量 1.5 CNY/USD &lt;br /&gt;春节期间倍率为0.7，本统计按日常价格计算。&lt;br /&gt;有日限/周限</t>
-  </si>
-  <si>
-    <t>购买19.9套餐</t>
-  </si>
-  <si>
-    <t>[FoxCode(狐狸)](https://foxcode.rjj.cc/auth/register?aff=6W5J31UI)</t>
-  </si>
-  <si>
-    <t>linkflow</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>需私聊上车，[站内地址](https://linux.do/t/topic/1092606)</t>
-  </si>
-  <si>
-    <t>汇率 &lt;br /&gt; 1$=?¥</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>最低消费（充值）&lt;br /&gt;（单位：¥）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>~~刚开业，优惠价为0.7RMB1刀~~优惠结束，现汇率改为1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>~~最低充值50~~最低充值100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>~~官渠暂时不可用~~ &lt;br /&gt;官渠恢复，倍率调整至7.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新开，后续价格可能会有波动</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -538,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -562,7 +576,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -571,7 +585,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>5</v>
@@ -611,10 +625,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <f>25*D3*E3</f>
@@ -624,7 +638,7 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F12" si="0">E3*D3</f>
@@ -634,53 +648,53 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <f>25*D4*E4</f>
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>0.84</v>
+        <v>1.4</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:C16" si="1">25*D5*E5</f>
+        <f t="shared" ref="C5:C18" si="1">25*D5*E5</f>
         <v>37.5</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>7.5</v>
@@ -693,49 +707,49 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <f t="shared" si="1"/>
-        <v>32.5</v>
+        <v>37.5</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
-        <v>19</v>
+      <c r="E6">
+        <v>1.5</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <f t="shared" si="1"/>
@@ -755,49 +769,49 @@
         <v>299</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <f>25*E8*D8</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G8">
         <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
@@ -807,7 +821,7 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
@@ -817,56 +831,56 @@
         <v>50</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" t="s">
-        <v>11</v>
+      <c r="E10">
+        <v>1.5</v>
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G10">
         <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
         <v>18.75</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -879,18 +893,18 @@
         <v>140</v>
       </c>
       <c r="H11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>150</v>
@@ -909,18 +923,18 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>150</v>
@@ -932,25 +946,25 @@
         <v>6</v>
       </c>
       <c r="F13">
-        <f t="shared" ref="F13:F16" si="2">E13*D13</f>
+        <f t="shared" ref="F13:F18" si="2">E13*D13</f>
         <v>2.0999999999999996</v>
       </c>
       <c r="G13">
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <v>150</v>
@@ -969,18 +983,18 @@
         <v>135</v>
       </c>
       <c r="H14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15">
         <v>150</v>
@@ -999,25 +1013,25 @@
         <v>468</v>
       </c>
       <c r="H15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2">
         <f t="shared" si="1"/>
         <v>13.750000000000002</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -1030,11 +1044,42 @@
         <v>220</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
-      </c>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>0.6</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="C18" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
